--- a/docs/qms/evidence-2026/17_NFR_Register/EM26-17_NFR_Register.xlsx
+++ b/docs/qms/evidence-2026/17_NFR_Register/EM26-17_NFR_Register.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NFR register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -485,32 +485,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>End-to-end grounded answer latency (chat)</t>
+          <t>Grounded chat answer latency</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>median ≤ 4 s; p95 ≤ 16 s</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>median 3,313 ms, p95 15,171 ms (concurrency 1, warm cache, n=30/cell)</t>
+          <t>median 3.31 s; p95 15.17 s (n=30)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e1_latency.json (harness eval/paper/e1_latency.py)</t>
+          <t>Paper harness E1 — eval/paper/results/e1_latency.json</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Retrieval share of total answer latency</t>
+          <t>Retrieval share of answer latency</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>Monitor only (no target)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2.8% of grounded latency</t>
+          <t>2.8 %</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>E1 decomposition</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Measured — notable: contradicts the project's own published assumption, recorded honestly in SUMMARY.json</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -559,12 +559,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tenant permission filter overhead</t>
+          <t>Tenant permission-filter overhead</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Negligible</t>
+          <t>≤ 1 ms</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -596,32 +596,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Voice: end of user speech → first audible reply</t>
+          <t>Voice: end of speech → first audible reply (dual-loop)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>median ≤ 1.0 s</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>median 635.8 ms, p95 894.0 ms (n=10, arm dual_i1)</t>
+          <t>median 636 ms; p95 894 ms (n=10)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e10_ablation.json</t>
+          <t>E10 ablation — e10_ablation.json; paper</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -633,32 +633,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Voice: first audible reply after the speculative-reply and GPU-STT work</t>
+          <t>Voice first reply after speculative-reply work</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>median ≤ 1.0 s</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0.14–0.49 s across 12 turns, two personas</t>
+          <t>0.14–0.49 s on GPU (12 turns, 2 personas); on CPU since 2026-10-06 — to re-measure</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Session test voice_e2e_v3.py; commit c2a6ed5 / ff29843</t>
+          <t>voice_e2e session test; commit ff29843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Measured — ~2× improvement on NFR-P04</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -675,17 +675,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>≤ 300 ms (GPU) / ≤ 1.6 s (CPU mode)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>~70–130 ms (GPU, CUDA graphs disabled), previously ~1.0–1.6 s (CPU)</t>
+          <t>70–130 ms on GPU; CPU mode since 2026-10-06 — to re-measure</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Commit ff29843; measured in-session</t>
+          <t>commit ff29843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Barge-in: user interrupt → assistant audio stops</t>
+          <t>Barge-in: interrupt → assistant audio stops</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>median ≤ 1.0 s</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>median 2,131 ms, p95 2,140.6 ms, success 1.00 (n=8)</t>
+          <t>median 2.13 s, success 1.00 (n=8)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e7_interaction.json</t>
+          <t>E7 — e7_interaction.json</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Measured — slowest NFR on record; candidate for a target and improvement</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -744,32 +744,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Citation precision — cited passages genuinely support the claim</t>
+          <t>Citation precision</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>≥ 0.98 (set in QO-01 QO-1, 2026-09-21)</t>
+          <t>≥ 0.98 (set in QO-01)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0.9792 (95% CI 0.938–1.02, n=36)</t>
+          <t>0.979 (n=36)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e5_grounding.json</t>
+          <t>E5 — e5_grounding.json</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Met (at the target boundary)</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -786,27 +786,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>≥ 0.80</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0.8256 (CI 0.713–0.938, n=43)</t>
+          <t>0.826 (n=43)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -818,32 +818,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fact support rate — required gold facts present in the answer</t>
+          <t>Fact support rate</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>≥ 0.80</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0.8152 (75 of 92 fact groups)</t>
+          <t>0.815 (75/92)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -855,32 +855,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Abstention accuracy — correctly declines when the corpus cannot answer</t>
+          <t>Abstention when the corpus cannot answer</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>≥ 0.80</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.7826 (CI 0.581–0.903, n=23)</t>
+          <t>0.783 (n=23)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Measured — weakest accuracy figure; directly tied to the product's central claim</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
@@ -892,96 +892,96 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Functional regression suite (52 golden questions, binary gate)</t>
+          <t>Golden regression suite (52 questions)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52/52 (gate at eval/run_eval.py:281)</t>
+          <t>≥ 49/52 (baseline 2026-08-06)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9/52 on 2026-09-22 — 43/43 retrieval questions fail with 0 citations because the evaluation corpus is absent; smalltalk 6/6, refusal 2/2, off-corpus 1/1. Historic: best 50/52 (2026-07-30), 49/52 (2026-08-06)</t>
+          <t>Blocked — corpus absent (9/52 by construction, 2026-09-22); run now aborts with the missing list</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>eval/reports/eval_20260922-135322.json</t>
+          <t>eval/run_eval.py; NC-2026-008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Gap — instrument inoperable. Raised as REG-04 NC-2026-008. Not a product regression; retrieval works when exercised directly</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NFR-S01</t>
+          <t>NFR-Q06</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>No cross-tenant content leakage in answers</t>
+          <t>Small talk answered without document citations</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>100 % of acceptance probes</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0 / 50 probes (CI 0–0.0714)</t>
+          <t>Pass on v1.4.1 (after fix e0ed4d0)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e3_permission.json</t>
+          <t>TC-EM-RAG-103 run 4</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NFR-S02</t>
+          <t>NFR-S01</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>No out-of-namespace hits on any retrieval path</t>
+          <t>No cross-tenant leakage in answers</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>0 leaks</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0 / 359 hits across all retrieval paths</t>
+          <t>0 / 50 probes</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e3b_path_isolation.json; fix commit 4e27109</t>
+          <t>E3 — e3_permission.json</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -991,451 +991,722 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Met — after a real defect; see §4</t>
+          <t>Kishan Haravu Pradeep</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NFR-S03</t>
+          <t>NFR-S02</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Prompt-injection containment</t>
+          <t>No out-of-namespace retrieval hits</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>not formally set</t>
+          <t>0 hits</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>attack success 0.102 with no defence (baseline arm), 98 attack documents</t>
+          <t>0 / 359 (all paths) after fix 4e27109</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>eval/paper/results/e4_injection.json</t>
+          <t>e3b_path_isolation.json</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Measured — partial; defended arms recorded in the file</t>
+          <t>Kishan Haravu Pradeep</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NFR-S04</t>
+          <t>NFR-S03</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Injection guards present in every prompt path</t>
+          <t>Prompt-injection success rate</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>All paths</t>
+          <t>≤ 5 % with defences</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5 unit tests asserting guards in analyzer / compress / contextualizer / RAG / strict prompts</t>
+          <t>10.2 % undefended → 5.1 % with evidence envelope</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>backend/tests/test_prompt_guards.py</t>
+          <t>E4 — e4_injection.json; paper</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Monitored</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NFR-R01</t>
+          <t>NFR-S04</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Service liveness monitored</t>
+          <t>Injection guards in every prompt path</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>All long-running services</t>
+          <t>All paths</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Health checks on 4 of 6 services (trtllm, backend, voice, ollama); frontend and cloudflared have none</t>
+          <t>5 unit tests, run by CI on every push</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>docker-compose.yml</t>
+          <t>test_prompt_guards.py; CI</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Partial gap</t>
+          <t>Richard Watson Stephen Amudha</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>NFR-R02</t>
+          <t>NFR-S05</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Automatic recovery from a fatal GPU fault</t>
+          <t>Public instance requires login</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Unattended recovery</t>
+          <t>Unauthenticated API → 401, always</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>/health returns 503 on a poisoned CUDA context; in-process watchdog exits; restart: unless-stopped recreates with a fresh context</t>
+          <t>401 from GitHub's network every 6 h; was off 2026-07-30 → 10-06 (NC-2026-009)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>backend/app/main.py:100-104; docker-compose.yml</t>
+          <t>public-gate-check workflow run 37561803121</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Monitored</t>
+          <t>Kishan Haravu Pradeep</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NFR-R03</t>
+          <t>NFR-S06</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Disk exhaustion from unbounded logs</t>
+          <t>Logout ends the session</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Bounded</t>
+          <t>Replayed token → 401</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Log rotation 50 MB × 5 on all six services</t>
+          <t>401 (fix e0ed4d0)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>docker-compose.yml (2026-09-22)</t>
+          <t>TC-EM-AUTH-101 AC-101.7 run 4</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Met — applies on next docker compose up -d</t>
+          <t>Kishan Haravu Pradeep</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NFR-R04</t>
+          <t>NFR-S07</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Customer data recoverable after loss</t>
+          <t>Only supported document types accepted</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tested restore within 6 months</t>
+          <t>Binary/unsupported → 415</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Restore exercised into a clean volume: integrity_check ok, 32 tables, 351 MB archive</t>
+          <t>415 (fix e0ed4d0)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>scripts/backup_data.sh / restore_data.sh</t>
+          <t>TC-EM-DOC-102 DOC-102.5 run 4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Kishan Haravu Pradeep</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>NFR-R05</t>
+          <t>NFR-S08</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Build reproducibility</t>
+          <t>Export gateway removes PII and keys</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Pinned dependencies</t>
+          <t>No sensitive value in redacted copy</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>nemo_toolkit pinned to commit 60ce9407, previously the moving branch @main which caused a production outage</t>
+          <t>Pass incl. sk-/pk- keys (fix e0ed4d0)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>backend/Dockerfile, voice/Dockerfile; outage commit 724fb98</t>
+          <t>TC-EM-EXP-108 run 4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Kishan Haravu Pradeep</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>NFR-D01</t>
+          <t>NFR-R01</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Customer data never leaves the customer perimeter</t>
+          <t>Health checks that exercise the function</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>All long-running services</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>All inference local; no cloud AI provider enabled; the single cloud image path (DOCGEN_IMAGE_BACKEND=nim) is disabled</t>
+          <t>4 of 6 services; Ollama check now makes a real embedding (2026-10-07); frontend/cloudflared none</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>docker-compose.yml; REG-02 §4</t>
+          <t>docker-compose.yml; NC-2026-016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Monitored</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>NFR-D02</t>
+          <t>NFR-R02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Encryption at rest</t>
+          <t>Automatic recovery from a fatal GPU fault</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unattended recovery</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>None. SQLite, uploads and FAISS indexes are unencrypted</t>
+          <t>/health 503 + watchdog + restart policy</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>REG-03 risk R-13</t>
+          <t>backend/app/main.py; docker-compose.yml</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Gap — accepted, disclosed</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NFR-D03</t>
+          <t>NFR-R03</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Data retention bounded</t>
+          <t>Bounded logs</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Per data class</t>
+          <t>50 MB × 5 per service</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>No retention policy exists; auto-store grows the corpus continuously (97.6% of chunks were auto-saved transcript at one measurement)</t>
+          <t>Applied to all six containers</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>REG-03 risk R-06; corpus_stats.json</t>
+          <t>docker inspect; REG-07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NFR-S02</t>
+          <t>NFR-R04</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Golden evaluation fell 50/52 → 42/52. Root cause: one retrieval path bypassed the namespace predicate, returning 10/10 out-of-namespace chunks under a tenant-scoped query. Pre-existing and latent; became visible only as the corpus grew.</t>
+          <t>Customer data recoverable</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Fixed (4e27109), all five paths audited, 0/359 out-of-namespace hits, suite restored to 49/52. Logged as REG-04 NC-2026-001.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>Restore tested ≤ 6 months; nightly off-site copy</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Restore verified 2026-09-22; checksum verified 2026-10-06; off-site schedule not installed</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>TC-EM-BKP-113</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NFR-Q05</t>
+          <t>NFR-R05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A retrieval feature measured *worse* than the baseline</t>
+          <t>Reproducible builds</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Disabled by default (2decb99) rather than retained on expectation</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>All dependencies pinned</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>NeMo pinned (60ce9407); ollama/cloudflared images unpinned</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Dockerfiles; REG-02</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NFR-R05</t>
+          <t>NFR-M01</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>A moving-branch dependency broke build and runtime</t>
+          <t>Automated regression on every change</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Root-caused, re-pinned, verified on a from-scratch rebuild (724fb98); permanently pinned 2026-09-22</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>Every push</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CI: backend 50, voice 131, type-check; proven to fail on a broken test</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CI runs 37561379960 / 37561804619</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>NFR-M02</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Running instance traceable to source</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Version + commit reported</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1.4.1 / f1b8445 on backend, voice and front end</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>/api/version; TC-EM-REL-106</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NFR-D01</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Customer data never leaves the perimeter</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Absolute</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>All inference local; no cloud AI path enabled</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>docker-compose.yml; REG-02</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>NFR-D02</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Encryption at rest</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Decision required</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>None (SQLite, uploads, indexes unencrypted)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>REG-03 R-13</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>NFR-D03</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Retention bounded per data class</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Per class, in days (decision)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>No policy</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>REG-03 R-06</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>NFR-S02</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Golden evaluation fell 50/52 → 42/52. Root cause: one retrieval path bypassed the namespace predicate, returning 10/10 out-of-namespace chunks under a tenant-scoped query. Pre-existing and latent; became visible only as the corpus grew.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Fixed (4e27109), all five paths audited, 0/359 out-of-namespace hits, suite restored to 49/52. Logged as REG-04 NC-2026-001.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>NFR-Q05</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A retrieval feature measured *worse* than the baseline</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Disabled by default (2decb99) rather than retained on expectation</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>NFR-R05</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A moving-branch dependency broke build and runtime</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Root-caused, re-pinned, verified on a from-scratch rebuild (724fb98); permanently pinned 2026-09-22</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>NFR-P05/P06</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Voice first-reply latency and STT decode time</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Re-engineered; measured improvement ~2× and ~10× respectively (ff29843, c2a6ed5)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
